--- a/04_Features/modules/preservation/c_data/preservation.xlsx
+++ b/04_Features/modules/preservation/c_data/preservation.xlsx
@@ -9,12 +9,13 @@
     <sheet name="preservation" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="arm_native" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="arm_sizes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="provenance" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t xml:space="preserve">reference</t>
   </si>
@@ -67,6 +68,9 @@
     <t xml:space="preserve">red</t>
   </si>
   <si>
+    <t xml:space="preserve">tan</t>
+  </si>
+  <si>
     <t xml:space="preserve">turquoise</t>
   </si>
   <si>
@@ -94,12 +98,12 @@
     <t xml:space="preserve">midnightblue</t>
   </si>
   <si>
+    <t xml:space="preserve">royalblue</t>
+  </si>
+  <si>
     <t xml:space="preserve">salmon</t>
   </si>
   <si>
-    <t xml:space="preserve">tan</t>
-  </si>
-  <si>
     <t xml:space="preserve">group</t>
   </si>
   <si>
@@ -107,6 +111,12 @@
   </si>
   <si>
     <t xml:space="preserve">n_subjects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fingerprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9e040a2492f9</t>
   </si>
 </sst>
 </file>
@@ -466,13 +476,13 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>103</v>
+        <v>134</v>
       </c>
       <c r="E2" t="n">
-        <v>7.64475186511778</v>
+        <v>15.8689009167862</v>
       </c>
       <c r="F2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -486,13 +496,13 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>211</v>
+        <v>174</v>
       </c>
       <c r="E3" t="n">
-        <v>18.604811262322</v>
+        <v>13.6951985878301</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -506,13 +516,13 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E4" t="n">
-        <v>11.7204736676479</v>
+        <v>13.9377153563755</v>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -526,13 +536,13 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="E5" t="n">
-        <v>11.305090585164</v>
+        <v>9.61056909100696</v>
       </c>
       <c r="F5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -546,13 +556,13 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="E6" t="n">
-        <v>8.31923695629347</v>
+        <v>11.1446269308373</v>
       </c>
       <c r="F6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -566,13 +576,13 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="E7" t="n">
-        <v>20.3273261746701</v>
+        <v>11.9795818996923</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -586,13 +596,13 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="E8" t="n">
-        <v>10.0073415920253</v>
+        <v>19.2255242072583</v>
       </c>
       <c r="F8" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -606,13 +616,13 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="E9" t="n">
-        <v>10.0201709843745</v>
+        <v>10.4469206753808</v>
       </c>
       <c r="F9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -626,13 +636,13 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>106</v>
+        <v>143</v>
       </c>
       <c r="E10" t="n">
-        <v>13.1868288996984</v>
+        <v>9.31605761813104</v>
       </c>
       <c r="F10" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -646,13 +656,13 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>361</v>
+        <v>58</v>
       </c>
       <c r="E11" t="n">
-        <v>35.9129807289818</v>
+        <v>8.40360311261215</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -666,33 +676,33 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>359</v>
       </c>
       <c r="E12" t="n">
-        <v>13.8725021487169</v>
+        <v>35.5667300714672</v>
       </c>
       <c r="F12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B13" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C13" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D13" t="n">
-        <v>103</v>
+        <v>159</v>
       </c>
       <c r="E13" t="n">
-        <v>17.7989901232668</v>
+        <v>10.6834207545962</v>
       </c>
       <c r="F13" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
@@ -703,16 +713,16 @@
         <v>6</v>
       </c>
       <c r="C14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>211</v>
+        <v>134</v>
       </c>
       <c r="E14" t="n">
-        <v>14.0463560738846</v>
+        <v>21.8803665625513</v>
       </c>
       <c r="F14" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -723,16 +733,16 @@
         <v>6</v>
       </c>
       <c r="C15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="E15" t="n">
-        <v>19.8031138980356</v>
+        <v>14.2149659611028</v>
       </c>
       <c r="F15" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
@@ -743,13 +753,13 @@
         <v>6</v>
       </c>
       <c r="C16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>134</v>
+        <v>164</v>
       </c>
       <c r="E16" t="n">
-        <v>12.4147478911714</v>
+        <v>17.287825345291</v>
       </c>
       <c r="F16" t="n">
         <v>9</v>
@@ -763,16 +773,16 @@
         <v>6</v>
       </c>
       <c r="C17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D17" t="n">
-        <v>69</v>
+        <v>156</v>
       </c>
       <c r="E17" t="n">
-        <v>13.0672253870546</v>
+        <v>15.0688049469731</v>
       </c>
       <c r="F17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -783,16 +793,16 @@
         <v>6</v>
       </c>
       <c r="C18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D18" t="n">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="E18" t="n">
-        <v>17.7098644060022</v>
+        <v>7.80223578942139</v>
       </c>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19">
@@ -803,16 +813,16 @@
         <v>6</v>
       </c>
       <c r="C19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D19" t="n">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="E19" t="n">
-        <v>12.1151872874356</v>
+        <v>12.6458977218998</v>
       </c>
       <c r="F19" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -823,16 +833,16 @@
         <v>6</v>
       </c>
       <c r="C20" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D20" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E20" t="n">
-        <v>13.9877356042199</v>
+        <v>18.0850621155421</v>
       </c>
       <c r="F20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -843,16 +853,16 @@
         <v>6</v>
       </c>
       <c r="C21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D21" t="n">
-        <v>106</v>
+        <v>68</v>
       </c>
       <c r="E21" t="n">
-        <v>23.7797330109817</v>
+        <v>11.6508662436632</v>
       </c>
       <c r="F21" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
@@ -863,16 +873,16 @@
         <v>6</v>
       </c>
       <c r="C22" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D22" t="n">
-        <v>361</v>
+        <v>143</v>
       </c>
       <c r="E22" t="n">
-        <v>32.4664461589214</v>
+        <v>13.4888813099376</v>
       </c>
       <c r="F22" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23">
@@ -883,16 +893,56 @@
         <v>6</v>
       </c>
       <c r="C23" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23" t="n">
+        <v>58</v>
+      </c>
+      <c r="E23" t="n">
+        <v>12.5162818013852</v>
+      </c>
+      <c r="F23" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" t="s">
         <v>18</v>
       </c>
-      <c r="D23" t="n">
-        <v>165</v>
-      </c>
-      <c r="E23" t="n">
-        <v>13.8653189997601</v>
-      </c>
-      <c r="F23" t="n">
-        <v>10</v>
+      <c r="D24" t="n">
+        <v>359</v>
+      </c>
+      <c r="E24" t="n">
+        <v>31.66413849947</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" t="n">
+        <v>159</v>
+      </c>
+      <c r="E25" t="n">
+        <v>21.8180594050802</v>
+      </c>
+      <c r="F25" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -926,7 +976,7 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2">
@@ -940,16 +990,16 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="E2" t="n">
-        <v>3.26327115653097</v>
+        <v>0.817772771368018</v>
       </c>
       <c r="F2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -963,16 +1013,16 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E3" t="n">
-        <v>8.56390748879768</v>
+        <v>14.1407646731401</v>
       </c>
       <c r="F3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -986,16 +1036,16 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E4" t="n">
-        <v>11.4403708700652</v>
+        <v>16.1925566307048</v>
       </c>
       <c r="F4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -1006,19 +1056,19 @@
         <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E5" t="n">
-        <v>7.88696353727924</v>
+        <v>5.96066158515587</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -1032,16 +1082,16 @@
         <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="E6" t="n">
-        <v>26.3419521731192</v>
+        <v>8.10161346166181</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -1055,16 +1105,16 @@
         <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E7" t="n">
-        <v>1.87341968751282</v>
+        <v>4.87125314633298</v>
       </c>
       <c r="F7" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -1075,19 +1125,19 @@
         <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D8" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="E8" t="n">
-        <v>4.42501958263082</v>
+        <v>5.49697845229475</v>
       </c>
       <c r="F8" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
@@ -1098,19 +1148,19 @@
         <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D9" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E9" t="n">
-        <v>6.58166563351445</v>
+        <v>5.53304430379803</v>
       </c>
       <c r="F9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
@@ -1121,19 +1171,19 @@
         <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="E10" t="n">
-        <v>3.18386520484002</v>
+        <v>6.62054929670967</v>
       </c>
       <c r="F10" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
@@ -1144,19 +1194,19 @@
         <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D11" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E11" t="n">
-        <v>1.87453058100512</v>
+        <v>4.66260456481193</v>
       </c>
       <c r="F11" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
@@ -1170,16 +1220,16 @@
         <v>13</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="E12" t="n">
-        <v>15.0872535741041</v>
+        <v>4.96511851817235</v>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="G12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -1190,19 +1240,19 @@
         <v>7</v>
       </c>
       <c r="C13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D13" t="n">
         <v>53</v>
       </c>
       <c r="E13" t="n">
-        <v>4.20546090516745</v>
+        <v>2.88481838091613</v>
       </c>
       <c r="F13" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
@@ -1216,16 +1266,16 @@
         <v>14</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="E14" t="n">
-        <v>3.55649810162138</v>
+        <v>6.98962640972996</v>
       </c>
       <c r="F14" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15">
@@ -1239,16 +1289,16 @@
         <v>15</v>
       </c>
       <c r="D15" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E15" t="n">
-        <v>15.0857718797711</v>
+        <v>3.74858278528429</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="G15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -1262,16 +1312,16 @@
         <v>16</v>
       </c>
       <c r="D16" t="n">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="E16" t="n">
-        <v>8.01308522393866</v>
+        <v>4.31099716850416</v>
       </c>
       <c r="F16" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="G16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -1282,19 +1332,19 @@
         <v>7</v>
       </c>
       <c r="C17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D17" t="n">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="E17" t="n">
-        <v>3.63840293609037</v>
+        <v>3.73133734989668</v>
       </c>
       <c r="F17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
@@ -1305,19 +1355,19 @@
         <v>7</v>
       </c>
       <c r="C18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D18" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E18" t="n">
-        <v>10.1831894503239</v>
+        <v>11.92351538265</v>
       </c>
       <c r="F18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
@@ -1331,16 +1381,16 @@
         <v>17</v>
       </c>
       <c r="D19" t="n">
-        <v>207</v>
+        <v>66</v>
       </c>
       <c r="E19" t="n">
-        <v>12.4067780887991</v>
+        <v>16.6189373532257</v>
       </c>
       <c r="F19" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20">
@@ -1354,39 +1404,39 @@
         <v>18</v>
       </c>
       <c r="D20" t="n">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="E20" t="n">
-        <v>6.01214845293346</v>
+        <v>30.0353793678079</v>
       </c>
       <c r="F20" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B21" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C21" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D21" t="n">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="E21" t="n">
-        <v>7.8112246488008</v>
+        <v>10.1167924308114</v>
       </c>
       <c r="F21" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G21" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
@@ -1397,19 +1447,19 @@
         <v>6</v>
       </c>
       <c r="C22" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D22" t="n">
-        <v>186</v>
+        <v>79</v>
       </c>
       <c r="E22" t="n">
-        <v>5.83376784198413</v>
+        <v>3.81770370639956</v>
       </c>
       <c r="F22" t="n">
         <v>12</v>
       </c>
       <c r="G22" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23">
@@ -1420,19 +1470,19 @@
         <v>6</v>
       </c>
       <c r="C23" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D23" t="n">
-        <v>149</v>
+        <v>215</v>
       </c>
       <c r="E23" t="n">
-        <v>4.79294778572968</v>
+        <v>5.78878100283896</v>
       </c>
       <c r="F23" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G23" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24">
@@ -1443,19 +1493,19 @@
         <v>6</v>
       </c>
       <c r="C24" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D24" t="n">
-        <v>47</v>
+        <v>152</v>
       </c>
       <c r="E24" t="n">
-        <v>5.1388010086203</v>
+        <v>3.28453573784779</v>
       </c>
       <c r="F24" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G24" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25">
@@ -1466,19 +1516,19 @@
         <v>6</v>
       </c>
       <c r="C25" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D25" t="n">
-        <v>123</v>
+        <v>43</v>
       </c>
       <c r="E25" t="n">
-        <v>10.5335357173769</v>
+        <v>6.50176836751429</v>
       </c>
       <c r="F25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G25" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26">
@@ -1489,19 +1539,19 @@
         <v>6</v>
       </c>
       <c r="C26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D26" t="n">
-        <v>79</v>
+        <v>123</v>
       </c>
       <c r="E26" t="n">
-        <v>5.23157253339458</v>
+        <v>12.2261818825243</v>
       </c>
       <c r="F26" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G26" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27">
@@ -1512,19 +1562,19 @@
         <v>6</v>
       </c>
       <c r="C27" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D27" t="n">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="E27" t="n">
-        <v>7.68520616463463</v>
+        <v>17.0515540340474</v>
       </c>
       <c r="F27" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28">
@@ -1535,19 +1585,19 @@
         <v>6</v>
       </c>
       <c r="C28" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D28" t="n">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="E28" t="n">
-        <v>7.48556341458288</v>
+        <v>3.52888830222598</v>
       </c>
       <c r="F28" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G28" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29">
@@ -1558,19 +1608,19 @@
         <v>6</v>
       </c>
       <c r="C29" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D29" t="n">
-        <v>88</v>
+        <v>42</v>
       </c>
       <c r="E29" t="n">
-        <v>16.2605648534057</v>
+        <v>1.33784963932367</v>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="G29" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30">
@@ -1581,19 +1631,19 @@
         <v>6</v>
       </c>
       <c r="C30" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D30" t="n">
-        <v>115</v>
+        <v>70</v>
       </c>
       <c r="E30" t="n">
-        <v>13.4362445588423</v>
+        <v>6.09941932324933</v>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G30" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31">
@@ -1607,16 +1657,16 @@
         <v>26</v>
       </c>
       <c r="D31" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="E31" t="n">
-        <v>3.41187528581256</v>
+        <v>9.82096894249115</v>
       </c>
       <c r="F31" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="G31" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32">
@@ -1627,19 +1677,19 @@
         <v>6</v>
       </c>
       <c r="C32" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="D32" t="n">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="E32" t="n">
-        <v>1.59415371548382</v>
+        <v>6.27499661214491</v>
       </c>
       <c r="F32" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G32" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33">
@@ -1650,19 +1700,19 @@
         <v>6</v>
       </c>
       <c r="C33" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D33" t="n">
-        <v>349</v>
+        <v>61</v>
       </c>
       <c r="E33" t="n">
-        <v>31.734045211765</v>
+        <v>3.73105769525978</v>
       </c>
       <c r="F33" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G33" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34">
@@ -1673,19 +1723,111 @@
         <v>6</v>
       </c>
       <c r="C34" t="s">
+        <v>16</v>
+      </c>
+      <c r="D34" t="n">
+        <v>108</v>
+      </c>
+      <c r="E34" t="n">
+        <v>9.88199115799199</v>
+      </c>
+      <c r="F34" t="n">
+        <v>6</v>
+      </c>
+      <c r="G34" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>7</v>
+      </c>
+      <c r="B35" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" t="s">
+        <v>28</v>
+      </c>
+      <c r="D35" t="n">
+        <v>45</v>
+      </c>
+      <c r="E35" t="n">
+        <v>5.5770669858474</v>
+      </c>
+      <c r="F35" t="n">
+        <v>7</v>
+      </c>
+      <c r="G35" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>7</v>
+      </c>
+      <c r="B36" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" t="s">
+        <v>17</v>
+      </c>
+      <c r="D36" t="n">
+        <v>54</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1.51945329493799</v>
+      </c>
+      <c r="F36" t="n">
+        <v>17</v>
+      </c>
+      <c r="G36" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>7</v>
+      </c>
+      <c r="B37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" t="s">
         <v>18</v>
       </c>
-      <c r="D34" t="n">
-        <v>126</v>
-      </c>
-      <c r="E34" t="n">
-        <v>3.40320248159551</v>
-      </c>
-      <c r="F34" t="n">
-        <v>11</v>
-      </c>
-      <c r="G34" t="n">
-        <v>14</v>
+      <c r="D37" t="n">
+        <v>352</v>
+      </c>
+      <c r="E37" t="n">
+        <v>28.8191002328122</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2</v>
+      </c>
+      <c r="G37" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>7</v>
+      </c>
+      <c r="B38" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" t="n">
+        <v>125</v>
+      </c>
+      <c r="E38" t="n">
+        <v>7.1422808450899</v>
+      </c>
+      <c r="F38" t="n">
+        <v>10</v>
+      </c>
+      <c r="G38" t="n">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1701,13 +1843,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2">
@@ -1730,6 +1872,27 @@
       </c>
       <c r="C3" t="n">
         <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
